--- a/sample-data/acme-sample-50.xlsx
+++ b/sample-data/acme-sample-50.xlsx
@@ -538,12 +538,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tejas Sunder</t>
+          <t>Ruth Mcneil</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tejas.sunder.581@acme.example</t>
+          <t>ruth.mcneil.5138@acme.example</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -553,24 +553,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Associate Account Executive</t>
+          <t>Principal Account Executive</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>42005</v>
+        <v>42006</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>46327</v>
@@ -581,28 +581,22 @@
       <c r="M2" t="n">
         <v>-5000</v>
       </c>
-      <c r="P2" t="n">
-        <v>719768</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>420336</v>
-      </c>
       <c r="R2" t="n">
-        <v>280530</v>
+        <v>81893</v>
       </c>
       <c r="V2" t="n">
-        <v>216810</v>
+        <v>22796</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HR-96108</t>
+          <t>HR-58701</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kristen Davis</t>
+          <t>Ria Schleich</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -612,20 +606,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>design</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lead Operations Analyst</t>
+          <t>Head of Design</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -634,38 +628,41 @@
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>42005</v>
+        <v>42011</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L3" t="n">
-        <v>29000</v>
+        <v>36200</v>
       </c>
       <c r="M3" t="n">
-        <v>363825</v>
+        <v>336000</v>
       </c>
       <c r="R3" t="n">
-        <v>77104</v>
+        <v>113233</v>
+      </c>
+      <c r="U3" t="n">
+        <v>65270</v>
       </c>
       <c r="V3" t="n">
-        <v>28294</v>
+        <v>67053</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HR-58701</t>
+          <t>HR-72009</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Varenya Bakshi</t>
+          <t>Rodney Figueroa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>varenya.bakshi.5643@acme.example</t>
+          <t>rodney.figueroa.6273@acme.example</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -675,71 +672,71 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Principal Engineer</t>
+          <t>Head of Customer Support</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>42005</v>
+        <v>42016</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="M4" t="n">
-        <v>6313860</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2450720</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1599987</v>
+        <v>262920</v>
+      </c>
+      <c r="N4" t="n">
+        <v>21051</v>
       </c>
       <c r="R4" t="n">
-        <v>2990103</v>
+        <v>89099</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50310</v>
       </c>
       <c r="V4" t="n">
-        <v>721028</v>
+        <v>42499</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HR-90977</t>
+          <t>HR-40255</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Matthew Holden</t>
+          <t>Ashley Bruce</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>matthew.holden.7537@acme.example</t>
+          <t>ashley.bruce.2208@acme.example</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>legal</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Senior Counsel</t>
+          <t>Head of Sales</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -747,16 +744,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>42005</v>
+        <v>42022</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>46327</v>
@@ -765,55 +762,52 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>238350</v>
+        <v>499170</v>
       </c>
       <c r="R5" t="n">
-        <v>48575</v>
-      </c>
-      <c r="T5" t="n">
-        <v>23903</v>
+        <v>150780</v>
       </c>
       <c r="V5" t="n">
-        <v>35026</v>
+        <v>39431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HR-82536</t>
+          <t>HR-22906</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jim Wright</t>
+          <t>Ekiya Koshy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jim.wright.9779@acme.example</t>
+          <t>ekiya.koshy.99@acme.example</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Head of Operations</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -825,46 +819,52 @@
         <v>46327</v>
       </c>
       <c r="L6" t="n">
-        <v>15900</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>243285</v>
+        <v>4998840</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1943115</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1240917</v>
       </c>
       <c r="R6" t="n">
-        <v>54538</v>
+        <v>2471098</v>
       </c>
       <c r="V6" t="n">
-        <v>20003</v>
+        <v>598981</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HR-96021</t>
+          <t>HR-90972</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jairaj Solanki</t>
+          <t>Yauvani De</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jairaj.solanki.210@acme.example</t>
+          <t>yauvani.de.7617@acme.example</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>data</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Principal Data Scientist</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -873,11 +873,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I7" s="1" t="n">
-        <v>42006</v>
+        <v>42030</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>46327</v>
@@ -886,53 +886,53 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5559435</v>
+        <v>3619350</v>
       </c>
       <c r="P7" t="n">
-        <v>2249475</v>
+        <v>1403080</v>
       </c>
       <c r="Q7" t="n">
-        <v>1382515</v>
+        <v>932354</v>
       </c>
       <c r="R7" t="n">
-        <v>1915218</v>
+        <v>1785986</v>
       </c>
       <c r="V7" t="n">
-        <v>696264</v>
+        <v>429373</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HR-96021</t>
+          <t>HR-90972</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David Thomas</t>
+          <t>Vihaan Divan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>david.thomas.2852@acme.example</t>
+          <t>vihaan.divan.7463@acme.example</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Principal Financial Analyst</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -941,54 +941,54 @@
         </is>
       </c>
       <c r="I8" s="1" t="n">
-        <v>42007</v>
+        <v>42034</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L8" t="n">
-        <v>15500</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>179550</v>
-      </c>
-      <c r="N8" t="n">
-        <v>14726</v>
+        <v>4039245</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1675338</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>985327</v>
       </c>
       <c r="R8" t="n">
-        <v>20054</v>
-      </c>
-      <c r="S8" t="n">
-        <v>37229</v>
+        <v>2018648</v>
       </c>
       <c r="V8" t="n">
-        <v>31207</v>
+        <v>508065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HR-87650</t>
+          <t>HR-18239</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Elijah Nagarajan</t>
+          <t>Theodore Sethi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>elijah.nagarajan.6990@acme.example</t>
+          <t>theodore.sethi.2802@acme.example</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Principal Operations Analyst</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1005,126 +1005,126 @@
         </is>
       </c>
       <c r="I9" s="1" t="n">
-        <v>42007</v>
+        <v>42037</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>478900</v>
       </c>
       <c r="M9" t="n">
-        <v>5848395</v>
+        <v>4008270</v>
       </c>
       <c r="P9" t="n">
-        <v>2380536</v>
+        <v>1537427</v>
       </c>
       <c r="Q9" t="n">
-        <v>1423461</v>
+        <v>995568</v>
       </c>
       <c r="R9" t="n">
-        <v>3038041</v>
+        <v>2021335</v>
       </c>
       <c r="V9" t="n">
-        <v>697738</v>
+        <v>492222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HR-46925</t>
+          <t>HR-17871</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rishi Deol</t>
+          <t>Janice Jefferson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rishi.deol.9177@acme.example</t>
+          <t>janice.jefferson.6789@acme.example</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>customer-support</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Associate HR Partner</t>
+          <t>Head of Customer Support</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I10" s="1" t="n">
-        <v>42007</v>
+        <v>42037</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L10" t="n">
-        <v>108900</v>
+        <v>21100</v>
       </c>
       <c r="M10" t="n">
-        <v>1837185</v>
-      </c>
-      <c r="P10" t="n">
-        <v>710772</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>468360</v>
+        <v>260085</v>
+      </c>
+      <c r="N10" t="n">
+        <v>21743</v>
       </c>
       <c r="R10" t="n">
-        <v>318593</v>
+        <v>94787</v>
+      </c>
+      <c r="S10" t="n">
+        <v>51180</v>
       </c>
       <c r="V10" t="n">
-        <v>214501</v>
+        <v>45642</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HR-92641</t>
+          <t>HR-95332</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Siya Balakrishnan</t>
+          <t>Stacey Parker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>siya.balakrishnan.5818@acme.example</t>
+          <t>stacey.parker.8544@acme.example</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Product Manager</t>
+          <t>Head of Engineering</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="I11" s="1" t="n">
-        <v>42009</v>
+        <v>42039</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>46327</v>
@@ -1142,53 +1142,50 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2492385</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1043233</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>599637</v>
+        <v>257250</v>
       </c>
       <c r="R11" t="n">
-        <v>403592</v>
+        <v>78531</v>
+      </c>
+      <c r="T11" t="n">
+        <v>24919</v>
       </c>
       <c r="V11" t="n">
-        <v>306730</v>
+        <v>37063</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HR-40255</t>
+          <t>HR-67193</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Joseph Mclaughlin</t>
+          <t>Howard Pugh</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>joseph.mclaughlin.8388@acme.example</t>
+          <t>howard.pugh.2057@acme.example</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>customer-support</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Associate Account Executive</t>
+          <t>Head of Customer Support</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1197,52 +1194,55 @@
         </is>
       </c>
       <c r="I12" s="1" t="n">
-        <v>42010</v>
+        <v>42041</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L12" t="n">
-        <v>32300</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>242760</v>
+        <v>175665</v>
       </c>
       <c r="R12" t="n">
-        <v>26697</v>
+        <v>53930</v>
+      </c>
+      <c r="T12" t="n">
+        <v>17465</v>
       </c>
       <c r="V12" t="n">
-        <v>19872</v>
+        <v>25171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HR-60120</t>
+          <t>HR-36257</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Madhavi Korpal</t>
+          <t>Jagat Sarraf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>madhavi.korpal.8436@acme.example</t>
+          <t>jagat.sarraf.6283@acme.example</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lead Engineer</t>
+          <t>Principal Account Executive</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1251,75 +1251,75 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I13" s="1" t="n">
-        <v>42010</v>
+        <v>42041</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>193200</v>
       </c>
       <c r="M13" t="n">
-        <v>5942790</v>
+        <v>2366175</v>
       </c>
       <c r="P13" t="n">
-        <v>2469575</v>
+        <v>936444</v>
       </c>
       <c r="Q13" t="n">
-        <v>1519936</v>
+        <v>590736</v>
       </c>
       <c r="R13" t="n">
-        <v>2022775</v>
+        <v>1204044</v>
       </c>
       <c r="V13" t="n">
-        <v>732783</v>
+        <v>284735</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HR-53290</t>
+          <t>HR-59439</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gavin Harris</t>
+          <t>Maud van Bruchem</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gavin.harris.9859@acme.example</t>
+          <t>maud.vanbruchem.9948@acme.example</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lead Account Executive</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I14" s="1" t="n">
-        <v>42010</v>
+        <v>42041</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>46327</v>
@@ -1328,111 +1328,114 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>181650</v>
+        <v>207060</v>
+      </c>
+      <c r="O14" t="n">
+        <v>17234</v>
       </c>
       <c r="R14" t="n">
-        <v>36491</v>
-      </c>
-      <c r="T14" t="n">
-        <v>18516</v>
+        <v>67103</v>
       </c>
       <c r="V14" t="n">
-        <v>26452</v>
+        <v>38821</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HR-25441</t>
+          <t>HR-96777</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Philip Reuter</t>
+          <t>Ridhi Chowdhury</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>philip.reuter.4665@acme.example</t>
+          <t>ridhi.chowdhury.7548@acme.example</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lead Engineer</t>
+          <t>Head of Marketing</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I15" s="1" t="n">
-        <v>42011</v>
+        <v>42044</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L15" t="n">
-        <v>20400</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>317625</v>
+        <v>4844280</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1953464</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1165839</v>
       </c>
       <c r="R15" t="n">
-        <v>65223</v>
-      </c>
-      <c r="U15" t="n">
-        <v>65747</v>
+        <v>2388494</v>
       </c>
       <c r="V15" t="n">
-        <v>61648</v>
+        <v>602055</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HR-64354</t>
+          <t>HR-72770</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bruce Cross</t>
+          <t>Anirudh Iyer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bruce.cross.220@acme.example</t>
+          <t>anirudh.iyer.8913@acme.example</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Associate Financial Analyst</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1441,7 +1444,7 @@
         </is>
       </c>
       <c r="I16" s="1" t="n">
-        <v>42012</v>
+        <v>42044</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>46327</v>
@@ -1450,110 +1453,110 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>116340</v>
+        <v>4593120</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1887170</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1138258</v>
       </c>
       <c r="R16" t="n">
-        <v>11961</v>
-      </c>
-      <c r="T16" t="n">
-        <v>11624</v>
+        <v>2347637</v>
       </c>
       <c r="V16" t="n">
-        <v>16753</v>
+        <v>564232</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HR-22906</t>
+          <t>HR-90809</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Robin Hawkins</t>
+          <t>Douglas Allan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>robin.hawkins.2244@acme.example</t>
+          <t>douglas.allan.9767@acme.example</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>data</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Principal Data Scientist</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I17" s="1" t="n">
-        <v>42012</v>
+        <v>42046</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L17" t="n">
-        <v>33700</v>
+        <v>13900</v>
       </c>
       <c r="M17" t="n">
-        <v>242970</v>
-      </c>
-      <c r="N17" t="n">
-        <v>19565</v>
+        <v>157290</v>
       </c>
       <c r="R17" t="n">
-        <v>61357</v>
-      </c>
-      <c r="S17" t="n">
-        <v>50798</v>
+        <v>53666</v>
+      </c>
+      <c r="T17" t="n">
+        <v>16353</v>
       </c>
       <c r="V17" t="n">
-        <v>41160</v>
+        <v>22885</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HR-28287</t>
+          <t>HR-72057</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stefan Zuijdveld</t>
+          <t>Tijn Schenk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>stefan.zuijdveld.2696@acme.example</t>
+          <t>tijn.schenk.5163@acme.example</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>product</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Head of Engineering</t>
+          <t>Principal Product Manager</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1566,7 +1569,7 @@
         </is>
       </c>
       <c r="I18" s="1" t="n">
-        <v>42012</v>
+        <v>42047</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>46327</v>
@@ -1575,50 +1578,50 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>528570</v>
+        <v>171150</v>
       </c>
       <c r="O18" t="n">
-        <v>44367</v>
+        <v>14082</v>
       </c>
       <c r="R18" t="n">
-        <v>177619</v>
+        <v>55222</v>
       </c>
       <c r="V18" t="n">
-        <v>99123</v>
+        <v>30211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HR-39664</t>
+          <t>HR-68177</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Albert Blake</t>
+          <t>Philip van Schevinghuizen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>albert.blake.5294@acme.example</t>
+          <t>philip.vanschevinghuizen.1972@acme.example</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>legal</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Associate Account Executive</t>
+          <t>Head of Legal</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1627,51 +1630,51 @@
         </is>
       </c>
       <c r="I19" s="1" t="n">
-        <v>42012</v>
+        <v>42048</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>25700</v>
       </c>
       <c r="M19" t="n">
-        <v>89355</v>
+        <v>258825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>20465</v>
       </c>
       <c r="R19" t="n">
-        <v>8582</v>
-      </c>
-      <c r="T19" t="n">
-        <v>8951</v>
+        <v>90807</v>
       </c>
       <c r="V19" t="n">
-        <v>12554</v>
+        <v>48216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HR-97433</t>
+          <t>HR-55040</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rayaan Verma</t>
+          <t>Guiseppe Winkler</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rayaan.verma.5507@acme.example</t>
+          <t>guiseppe.winkler.2349@acme.example</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>design</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Principal Account Executive</t>
+          <t>Principal Designer</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1679,7 +1682,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1688,71 +1691,68 @@
         </is>
       </c>
       <c r="I20" s="1" t="n">
-        <v>42012</v>
+        <v>42055</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L20" t="n">
-        <v>920400</v>
+        <v>14500</v>
       </c>
       <c r="M20" t="n">
-        <v>6747615</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2669379</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1604304</v>
+        <v>147000</v>
       </c>
       <c r="R20" t="n">
-        <v>3532793</v>
+        <v>48230</v>
+      </c>
+      <c r="U20" t="n">
+        <v>28347</v>
       </c>
       <c r="V20" t="n">
-        <v>772522</v>
+        <v>30129</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HR-43071</t>
+          <t>HR-28378</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adelheid Hofmann</t>
+          <t>Brian Elliott</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>adelheid.hofmann.8983@acme.example</t>
+          <t>brian.elliott.4579@acme.example</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>legal</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Senior Counsel</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I21" s="1" t="n">
-        <v>42012</v>
+        <v>42069</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>46327</v>
@@ -1761,59 +1761,56 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>181335</v>
+        <v>361830</v>
       </c>
       <c r="R21" t="n">
-        <v>35219</v>
-      </c>
-      <c r="U21" t="n">
-        <v>37080</v>
+        <v>112712</v>
       </c>
       <c r="V21" t="n">
-        <v>37234</v>
+        <v>29285</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HR-38140</t>
+          <t>HR-68458</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Myriam Eigenwillig</t>
+          <t>Ikbal Luthra</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>myriam.eigenwillig.8172@acme.example</t>
+          <t>ikbal.luthra.4856@acme.example</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Senior HR Partner</t>
+          <t>Head of Sales</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I22" s="1" t="n">
-        <v>42013</v>
+        <v>42069</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>46327</v>
@@ -1822,50 +1819,53 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>143535</v>
+        <v>6069000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2436058</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1455023</v>
       </c>
       <c r="R22" t="n">
-        <v>29531</v>
-      </c>
-      <c r="U22" t="n">
-        <v>29931</v>
+        <v>3070522</v>
       </c>
       <c r="V22" t="n">
-        <v>29445</v>
+        <v>697825</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HR-16447</t>
+          <t>HR-28147</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Claus-Peter Zirme</t>
+          <t>Jason Clark</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>clauspeter.zirme.8968@acme.example</t>
+          <t>jason.clark.1000@acme.example</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Head of Finance</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1874,59 +1874,62 @@
         </is>
       </c>
       <c r="I23" s="1" t="n">
-        <v>42013</v>
+        <v>42071</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L23" t="n">
-        <v>13700</v>
+        <v>53500</v>
       </c>
       <c r="M23" t="n">
-        <v>179970</v>
+        <v>433755</v>
+      </c>
+      <c r="N23" t="n">
+        <v>34716</v>
       </c>
       <c r="R23" t="n">
-        <v>40434</v>
-      </c>
-      <c r="U23" t="n">
-        <v>35232</v>
+        <v>149772</v>
+      </c>
+      <c r="S23" t="n">
+        <v>86030</v>
       </c>
       <c r="V23" t="n">
-        <v>34301</v>
+        <v>71859</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HR-48314</t>
+          <t>HR-93543</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Iain Williams</t>
+          <t>Anmol Din</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>iain.williams.3440@acme.example</t>
+          <t>anmol.din.4613@acme.example</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Associate Marketing Specialist</t>
+          <t>Principal Financial Analyst</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1935,59 +1938,62 @@
         </is>
       </c>
       <c r="I24" s="1" t="n">
-        <v>42014</v>
+        <v>42073</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L24" t="n">
-        <v>4500</v>
+        <v>173100</v>
       </c>
       <c r="M24" t="n">
-        <v>79485</v>
+        <v>1627710</v>
+      </c>
+      <c r="P24" t="n">
+        <v>680436</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>426801</v>
       </c>
       <c r="R24" t="n">
-        <v>8385</v>
-      </c>
-      <c r="T24" t="n">
-        <v>7907</v>
+        <v>906879</v>
       </c>
       <c r="V24" t="n">
-        <v>11194</v>
+        <v>199721</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HR-45196</t>
+          <t>HR-35944</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Keya Bassi</t>
+          <t>Feline van Dam</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>keya.bassi.4549@acme.example</t>
+          <t>feline.vandam.786@acme.example</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>legal</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Senior Counsel</t>
+          <t>Head of Marketing</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1996,7 +2002,7 @@
         </is>
       </c>
       <c r="I25" s="1" t="n">
-        <v>42014</v>
+        <v>42077</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>46327</v>
@@ -2005,62 +2011,59 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4965345</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1901174</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1302293</v>
+        <v>264390</v>
+      </c>
+      <c r="O25" t="n">
+        <v>21596</v>
       </c>
       <c r="R25" t="n">
-        <v>1704212</v>
+        <v>88908</v>
       </c>
       <c r="V25" t="n">
-        <v>574504</v>
+        <v>46359</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HR-39118</t>
+          <t>HR-38816</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sara Stanley</t>
+          <t>Akshay Khatri</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sara.stanley.6019@acme.example</t>
+          <t>akshay.khatri.898@acme.example</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Senior Product Manager</t>
+          <t>Principal Financial Analyst</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I26" s="1" t="n">
-        <v>42014</v>
+        <v>42079</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>46327</v>
@@ -2069,32 +2072,35 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>150675</v>
+        <v>3665550</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1393608</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>873492</v>
       </c>
       <c r="R26" t="n">
-        <v>29378</v>
-      </c>
-      <c r="T26" t="n">
-        <v>14489</v>
+        <v>1858515</v>
       </c>
       <c r="V26" t="n">
-        <v>21161</v>
+        <v>435393</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HR-88097</t>
+          <t>HR-45043</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nandini Ramakrishnan</t>
+          <t>Zehaan Bhatti</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nandini.ramakrishnan.7972@acme.example</t>
+          <t>zehaan.bhatti.7595@acme.example</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2104,11 +2110,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2117,62 +2123,62 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I27" s="1" t="n">
-        <v>42016</v>
+        <v>42080</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>426900</v>
       </c>
       <c r="M27" t="n">
-        <v>1941660</v>
+        <v>4477620</v>
       </c>
       <c r="P27" t="n">
-        <v>800584</v>
+        <v>1763705</v>
       </c>
       <c r="Q27" t="n">
-        <v>492369</v>
+        <v>1079225</v>
       </c>
       <c r="R27" t="n">
-        <v>328655</v>
+        <v>2406915</v>
       </c>
       <c r="V27" t="n">
-        <v>233154</v>
+        <v>547733</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HR-27899</t>
+          <t>HR-78094</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gilbert Herrmann</t>
+          <t>Liselotte Hermann</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>gilbert.herrmann.6547@acme.example</t>
+          <t>liselotte.hermann.6135@acme.example</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Principal Marketing Specialist</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2181,45 +2187,45 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I28" s="1" t="n">
-        <v>42017</v>
+        <v>42082</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>19700</v>
       </c>
       <c r="M28" t="n">
-        <v>173460</v>
+        <v>141330</v>
       </c>
       <c r="R28" t="n">
-        <v>17953</v>
+        <v>48535</v>
       </c>
       <c r="U28" t="n">
-        <v>34675</v>
+        <v>28170</v>
       </c>
       <c r="V28" t="n">
-        <v>33577</v>
+        <v>27372</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HR-40380</t>
+          <t>HR-39498</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jacob Hawkins</t>
+          <t>Brandon Ellis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jacob.hawkins.8621@acme.example</t>
+          <t>brandon.ellis.3026@acme.example</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2229,11 +2235,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lead Account Executive</t>
+          <t>Principal Account Executive</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2246,41 +2252,41 @@
         </is>
       </c>
       <c r="I29" s="1" t="n">
-        <v>42017</v>
+        <v>42083</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>15500</v>
       </c>
       <c r="M29" t="n">
-        <v>204225</v>
+        <v>138810</v>
       </c>
       <c r="R29" t="n">
-        <v>38957</v>
+        <v>46683</v>
       </c>
       <c r="T29" t="n">
-        <v>19959</v>
+        <v>14391</v>
       </c>
       <c r="V29" t="n">
-        <v>29461</v>
+        <v>18872</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HR-90972</t>
+          <t>HR-72313</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ellen Thornton</t>
+          <t>Luke Sundaram</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ellen.thornton.9655@acme.example</t>
+          <t>luke.sundaram.6245@acme.example</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2290,71 +2296,71 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Head of Engineering</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I30" s="1" t="n">
-        <v>42017</v>
+        <v>42083</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L30" t="n">
-        <v>15900</v>
+        <v>324500</v>
       </c>
       <c r="M30" t="n">
-        <v>226170</v>
-      </c>
-      <c r="N30" t="n">
-        <v>18811</v>
+        <v>5409915</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2187003</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1324505</v>
       </c>
       <c r="R30" t="n">
-        <v>25102</v>
-      </c>
-      <c r="S30" t="n">
-        <v>44492</v>
+        <v>2699616</v>
       </c>
       <c r="V30" t="n">
-        <v>36898</v>
+        <v>656486</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HR-13700</t>
+          <t>HR-16650</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Leonard Söding</t>
+          <t>Dave Takkelenburg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>leonard.soding.2249@acme.example</t>
+          <t>dave.takkelenburg.6250@acme.example</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>customer-support</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Principal Engineer</t>
+          <t>Principal Support Specialist</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2362,7 +2368,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2371,7 +2377,7 @@
         </is>
       </c>
       <c r="I31" s="1" t="n">
-        <v>42018</v>
+        <v>42093</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>46327</v>
@@ -2380,22 +2386,22 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>281505</v>
+        <v>97020</v>
+      </c>
+      <c r="O31" t="n">
+        <v>7979</v>
       </c>
       <c r="R31" t="n">
-        <v>86978</v>
-      </c>
-      <c r="U31" t="n">
-        <v>58497</v>
+        <v>31112</v>
       </c>
       <c r="V31" t="n">
-        <v>56085</v>
+        <v>16949</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HR-78814</t>
+          <t>HR-83388</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2405,7 +2411,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>margaret.johnson.10001@acme.example</t>
+          <t>margaret.johnson.15001@acme.example</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2415,11 +2421,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2432,110 +2438,110 @@
         </is>
       </c>
       <c r="I32" s="1" t="n">
-        <v>42844</v>
+        <v>46250</v>
       </c>
       <c r="L32" t="n">
-        <v>11400</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>113600</v>
+        <v>73300</v>
       </c>
       <c r="R32" t="n">
-        <v>11883</v>
+        <v>7520</v>
       </c>
       <c r="V32" t="n">
-        <v>9366</v>
+        <v>5664</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HR-76595</t>
+          <t>HR-80961</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marcus Dowerg</t>
+          <t>Dayita Bakshi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>marcus.dowerg.10002@acme.example</t>
+          <t>dayita.bakshi.15002@acme.example</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>customer-support</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Senior Support Specialist</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I33" s="1" t="n">
-        <v>45105</v>
-      </c>
-      <c r="J33" s="1" t="n">
-        <v>45735</v>
+        <v>43726</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>78300</v>
+        <v>1147700</v>
+      </c>
+      <c r="P33" t="n">
+        <v>439744</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>280991</v>
       </c>
       <c r="R33" t="n">
-        <v>15035</v>
-      </c>
-      <c r="U33" t="n">
-        <v>15002</v>
+        <v>189857</v>
       </c>
       <c r="V33" t="n">
-        <v>15312</v>
+        <v>141485</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HR-63670</t>
+          <t>HR-67280</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dayita Bakshi</t>
+          <t>Laksh Konda</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dayita.bakshi.10003@acme.example</t>
+          <t>laksh.konda.15003@acme.example</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>customer-support</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Associate Designer</t>
+          <t>Senior Support Specialist</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2544,55 +2550,55 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I34" s="1" t="n">
-        <v>42589</v>
+        <v>44841</v>
       </c>
       <c r="L34" t="n">
-        <v>48200</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>548200</v>
+        <v>811800</v>
       </c>
       <c r="P34" t="n">
-        <v>230014</v>
+        <v>333682</v>
       </c>
       <c r="Q34" t="n">
-        <v>138969</v>
+        <v>197451</v>
       </c>
       <c r="R34" t="n">
-        <v>92021</v>
+        <v>139348</v>
       </c>
       <c r="V34" t="n">
-        <v>64570</v>
+        <v>95611</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HR-72171</t>
+          <t>HR-76311</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Laksh Konda</t>
+          <t>Isaac Dewan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>laksh.konda.10004@acme.example</t>
+          <t>isaac.dewan.15004@acme.example</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2609,113 +2615,110 @@
         </is>
       </c>
       <c r="I35" s="1" t="n">
-        <v>45276</v>
+        <v>45775</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1078600</v>
+        <v>891300</v>
       </c>
       <c r="P35" t="n">
-        <v>416462</v>
+        <v>353745</v>
       </c>
       <c r="Q35" t="n">
-        <v>260481</v>
+        <v>213099</v>
       </c>
       <c r="R35" t="n">
-        <v>171190</v>
+        <v>138691</v>
       </c>
       <c r="V35" t="n">
-        <v>130121</v>
+        <v>109317</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HR-85966</t>
+          <t>HR-91004</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Maja Heere</t>
+          <t>Donald Walker</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>maja.heere.10005@acme.example</t>
+          <t>donald.walker.15005@acme.example</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>customer-support</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lead Support Specialist</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I36" s="1" t="n">
-        <v>44409</v>
+        <v>45546</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>59200</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4584</v>
+        <v>82200</v>
       </c>
       <c r="R36" t="n">
-        <v>12896</v>
+        <v>8564</v>
       </c>
       <c r="V36" t="n">
-        <v>10286</v>
+        <v>6641</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HR-77346</t>
+          <t>HR-81797</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Isaac Dewan</t>
+          <t>Charan Chahal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>isaac.dewan.10006@acme.example</t>
+          <t>charan.chahal.15006@acme.example</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Principal Engineer</t>
+          <t>Associate Operations Analyst</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2728,41 +2731,41 @@
         </is>
       </c>
       <c r="I37" s="1" t="n">
-        <v>44524</v>
+        <v>46200</v>
       </c>
       <c r="L37" t="n">
-        <v>341500</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2771900</v>
+        <v>899900</v>
       </c>
       <c r="P37" t="n">
-        <v>1143799</v>
+        <v>361753</v>
       </c>
       <c r="Q37" t="n">
-        <v>726098</v>
+        <v>219689</v>
       </c>
       <c r="R37" t="n">
-        <v>1499126</v>
+        <v>143707</v>
       </c>
       <c r="V37" t="n">
-        <v>336174</v>
+        <v>105955</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HR-30950</t>
+          <t>HR-32393</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Charan Chahal</t>
+          <t>Nancy Rhodes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>charan.chahal.10007@acme.example</t>
+          <t>nancy.rhodes.15007@acme.example</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2772,68 +2775,68 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Support Specialist</t>
+          <t>Senior Support Specialist</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I38" s="1" t="n">
-        <v>45703</v>
+        <v>45055</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="M38" t="n">
-        <v>765100</v>
-      </c>
-      <c r="P38" t="n">
-        <v>297780</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>185923</v>
+        <v>58800</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4817</v>
       </c>
       <c r="R38" t="n">
-        <v>119521</v>
+        <v>7099</v>
+      </c>
+      <c r="S38" t="n">
+        <v>11743</v>
       </c>
       <c r="V38" t="n">
-        <v>89407</v>
+        <v>10219</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HR-75565</t>
+          <t>HR-79904</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Udyati Balay</t>
+          <t>Stephanie Miller</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>udyati.balay.10008@acme.example</t>
+          <t>stephanie.miller.15008@acme.example</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>data</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Senior Operations Analyst</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2841,7 +2844,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2850,112 +2853,103 @@
         </is>
       </c>
       <c r="I39" s="1" t="n">
-        <v>45879</v>
+        <v>45296</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1304300</v>
-      </c>
-      <c r="P39" t="n">
-        <v>517733</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>325000</v>
+        <v>104500</v>
       </c>
       <c r="R39" t="n">
-        <v>422506</v>
+        <v>10391</v>
       </c>
       <c r="V39" t="n">
-        <v>162177</v>
+        <v>8662</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HR-89690</t>
+          <t>HR-95024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Amruta Chander</t>
+          <t>Marcus Dowerg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>amruta.chander.10009@acme.example</t>
+          <t>marcus.dowerg.15009@acme.example</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Lead Operations Analyst</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I40" s="1" t="n">
-        <v>44051</v>
+        <v>44880</v>
       </c>
       <c r="L40" t="n">
-        <v>71500</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1204600</v>
-      </c>
-      <c r="P40" t="n">
-        <v>494058</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>293211</v>
+        <v>47900</v>
       </c>
       <c r="R40" t="n">
-        <v>196065</v>
+        <v>4655</v>
+      </c>
+      <c r="U40" t="n">
+        <v>9567</v>
       </c>
       <c r="V40" t="n">
-        <v>142968</v>
+        <v>9157</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HR-48320</t>
+          <t>HR-50914</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Frances Griffiths</t>
+          <t>Javier Johnson</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>frances.griffiths.10010@acme.example</t>
+          <t>javier.johnson.15010@acme.example</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>it</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Associate Account Executive</t>
+          <t>Associate IT Engineer</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2963,65 +2957,62 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I41" s="1" t="n">
-        <v>42484</v>
+        <v>45237</v>
       </c>
       <c r="L41" t="n">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>39400</v>
+        <v>83800</v>
       </c>
       <c r="R41" t="n">
-        <v>4447</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3775</v>
+        <v>8180</v>
       </c>
       <c r="V41" t="n">
-        <v>5370</v>
+        <v>6818</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HR-93205</t>
+          <t>HR-98767</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ashley Smith</t>
+          <t>Daniel Wagner</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ashley.smith.10011@acme.example</t>
+          <t>daniel.wagner.15011@acme.example</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Principal Account Executive</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3030,56 +3021,53 @@
         </is>
       </c>
       <c r="I42" s="1" t="n">
-        <v>44462</v>
+        <v>44318</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>59900</v>
+        <v>176100</v>
       </c>
       <c r="R42" t="n">
-        <v>6016</v>
-      </c>
-      <c r="T42" t="n">
-        <v>5837</v>
+        <v>35795</v>
       </c>
       <c r="V42" t="n">
-        <v>8220</v>
+        <v>14706</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HR-61129</t>
+          <t>HR-64553</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amelia Schellekens</t>
+          <t>Alyssa Gonzalez</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>amelia.schellekens.10012@acme.example</t>
+          <t>alyssa.gonzalez.15012@acme.example</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>customer-support</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Principal Engineer</t>
+          <t>Senior Support Specialist</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3088,48 +3076,45 @@
         </is>
       </c>
       <c r="I43" s="1" t="n">
-        <v>42881</v>
+        <v>45817</v>
       </c>
       <c r="L43" t="n">
-        <v>12000</v>
+        <v>12900</v>
       </c>
       <c r="M43" t="n">
-        <v>142800</v>
-      </c>
-      <c r="O43" t="n">
-        <v>11430</v>
+        <v>101800</v>
       </c>
       <c r="R43" t="n">
-        <v>51511</v>
+        <v>23819</v>
       </c>
       <c r="V43" t="n">
-        <v>24532</v>
+        <v>8473</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HR-29837</t>
+          <t>HR-31165</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Diane Newman</t>
+          <t>Alida Weihmann</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>diane.newman.10013@acme.example</t>
+          <t>alida.weihmann.15013@acme.example</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Associate Account Executive</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -3137,7 +3122,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3146,38 +3131,38 @@
         </is>
       </c>
       <c r="I44" s="1" t="n">
-        <v>43218</v>
+        <v>45855</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>34400</v>
+        <v>44500</v>
       </c>
       <c r="R44" t="n">
-        <v>3569</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3497</v>
+        <v>4306</v>
+      </c>
+      <c r="U44" t="n">
+        <v>8600</v>
       </c>
       <c r="V44" t="n">
-        <v>5044</v>
+        <v>8822</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HR-47292</t>
+          <t>HR-49807</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gijs Nek</t>
+          <t>Maja Heere</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>gijs.nek.10014@acme.example</t>
+          <t>maja.heere.15014@acme.example</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3187,11 +3172,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Senior Financial Analyst</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3200,60 +3185,60 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I45" s="1" t="n">
-        <v>44037</v>
+        <v>44871</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>59600</v>
+        <v>55900</v>
       </c>
       <c r="O45" t="n">
-        <v>4919</v>
+        <v>4604</v>
       </c>
       <c r="R45" t="n">
-        <v>6145</v>
+        <v>6271</v>
       </c>
       <c r="V45" t="n">
-        <v>10399</v>
+        <v>10532</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HR-71801</t>
+          <t>HR-75902</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Denise Walker</t>
+          <t>Marie Gardner</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>denise.walker.10015@acme.example</t>
+          <t>marie.gardner.15015@acme.example</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Principal Account Executive</t>
+          <t>Head of Operations</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3262,51 +3247,45 @@
         </is>
       </c>
       <c r="I46" s="1" t="n">
-        <v>44144</v>
+        <v>44179</v>
       </c>
       <c r="L46" t="n">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>242900</v>
-      </c>
-      <c r="N46" t="n">
-        <v>20265</v>
+        <v>323400</v>
       </c>
       <c r="R46" t="n">
-        <v>87550</v>
-      </c>
-      <c r="S46" t="n">
-        <v>47388</v>
+        <v>97393</v>
       </c>
       <c r="V46" t="n">
-        <v>39235</v>
+        <v>26440</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HR-98949</t>
+          <t>HR-59468</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Janani Kaul</t>
+          <t>Siddharth Balay</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>janani.kaul.10016@acme.example</t>
+          <t>siddharth.balay.15016@acme.example</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>customer-support</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Support Specialist</t>
+          <t>HR Partner</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -3319,100 +3298,106 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I47" s="1" t="n">
-        <v>43025</v>
+        <v>45749</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>795700</v>
+        <v>1083400</v>
       </c>
       <c r="P47" t="n">
-        <v>315174</v>
+        <v>428123</v>
       </c>
       <c r="Q47" t="n">
-        <v>194860</v>
+        <v>277571</v>
       </c>
       <c r="R47" t="n">
-        <v>132082</v>
+        <v>173724</v>
       </c>
       <c r="V47" t="n">
-        <v>93583</v>
+        <v>133723</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HR-56394</t>
+          <t>HR-33930</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nancy Rhodes</t>
+          <t>Alexander Chander</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nancy.rhodes.10017@acme.example</t>
+          <t>alexander.chander.15017@acme.example</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lead IT Engineer</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I48" s="1" t="n">
-        <v>42699</v>
+        <v>44287</v>
       </c>
       <c r="L48" t="n">
-        <v>31300</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>215900</v>
+        <v>715900</v>
+      </c>
+      <c r="P48" t="n">
+        <v>291308</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>174047</v>
       </c>
       <c r="R48" t="n">
-        <v>50767</v>
+        <v>113080</v>
       </c>
       <c r="V48" t="n">
-        <v>17195</v>
+        <v>85173</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HR-32418</t>
+          <t>HR-25691</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Aleksandr Weihmann</t>
+          <t>Stanley Griffiths</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>aleksandr.weihmann.10018@acme.example</t>
+          <t>stanley.griffiths.15018@acme.example</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3430,7 +3415,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3439,51 +3424,48 @@
         </is>
       </c>
       <c r="I49" s="1" t="n">
-        <v>45810</v>
-      </c>
-      <c r="J49" s="1" t="n">
-        <v>45967</v>
+        <v>45079</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>97700</v>
+        <v>72400</v>
       </c>
       <c r="R49" t="n">
-        <v>20335</v>
-      </c>
-      <c r="U49" t="n">
-        <v>20306</v>
+        <v>7198</v>
+      </c>
+      <c r="T49" t="n">
+        <v>7283</v>
       </c>
       <c r="V49" t="n">
-        <v>19434</v>
+        <v>10455</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HR-24695</t>
+          <t>HR-99454</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zayyan Bala</t>
+          <t>Ikbal Kaul</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>zayyan.bala.10019@acme.example</t>
+          <t>ikbal.kaul.15019@acme.example</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>legal</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Counsel</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -3500,83 +3482,80 @@
         </is>
       </c>
       <c r="I50" s="1" t="n">
-        <v>44276</v>
+        <v>46231</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1106800</v>
+        <v>1191900</v>
       </c>
       <c r="P50" t="n">
-        <v>424014</v>
+        <v>465876</v>
       </c>
       <c r="Q50" t="n">
-        <v>270771</v>
+        <v>292603</v>
       </c>
       <c r="R50" t="n">
-        <v>183653</v>
+        <v>186539</v>
       </c>
       <c r="V50" t="n">
-        <v>135558</v>
+        <v>141706</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HR-93846</t>
+          <t>HR-25797</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Collin Goyaerts van Waderle</t>
+          <t>Connie Lawrence</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>collin.goyaertsvanwaderle.10020@acme.example</t>
+          <t>connie.lawrence.15020@acme.example</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>data</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I51" s="1" t="n">
-        <v>45121</v>
+        <v>46156</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>87500</v>
-      </c>
-      <c r="O51" t="n">
-        <v>7027</v>
+        <v>129100</v>
       </c>
       <c r="R51" t="n">
-        <v>18476</v>
+        <v>13141</v>
       </c>
       <c r="V51" t="n">
-        <v>15727</v>
+        <v>10229</v>
       </c>
     </row>
   </sheetData>

--- a/sample-data/acme-sample-50.xlsx
+++ b/sample-data/acme-sample-50.xlsx
@@ -2499,19 +2499,19 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1147700</v>
+        <v>2327700</v>
       </c>
       <c r="P33" t="n">
-        <v>439744</v>
+        <v>891863</v>
       </c>
       <c r="Q33" t="n">
-        <v>280991</v>
+        <v>569890</v>
       </c>
       <c r="R33" t="n">
-        <v>189857</v>
+        <v>770113</v>
       </c>
       <c r="V33" t="n">
-        <v>141485</v>
+        <v>286951</v>
       </c>
     </row>
     <row r="34">
@@ -2560,19 +2560,19 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>811800</v>
+        <v>1236300</v>
       </c>
       <c r="P34" t="n">
-        <v>333682</v>
+        <v>508169</v>
       </c>
       <c r="Q34" t="n">
-        <v>197451</v>
+        <v>300701</v>
       </c>
       <c r="R34" t="n">
-        <v>139348</v>
+        <v>424429</v>
       </c>
       <c r="V34" t="n">
-        <v>95611</v>
+        <v>145607</v>
       </c>
     </row>
     <row r="35">
@@ -2621,19 +2621,19 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>891300</v>
+        <v>948400</v>
       </c>
       <c r="P35" t="n">
-        <v>353745</v>
+        <v>376407</v>
       </c>
       <c r="Q35" t="n">
-        <v>213099</v>
+        <v>226751</v>
       </c>
       <c r="R35" t="n">
-        <v>138691</v>
+        <v>147576</v>
       </c>
       <c r="V35" t="n">
-        <v>109317</v>
+        <v>116320</v>
       </c>
     </row>
     <row r="36">
@@ -2682,13 +2682,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>82200</v>
+        <v>89800</v>
       </c>
       <c r="R36" t="n">
-        <v>8564</v>
+        <v>9356</v>
       </c>
       <c r="V36" t="n">
-        <v>6641</v>
+        <v>7255</v>
       </c>
     </row>
     <row r="37">
@@ -2795,22 +2795,22 @@
         <v>45055</v>
       </c>
       <c r="L38" t="n">
-        <v>7100</v>
+        <v>10200</v>
       </c>
       <c r="M38" t="n">
-        <v>58800</v>
+        <v>84400</v>
       </c>
       <c r="N38" t="n">
-        <v>4817</v>
+        <v>6914</v>
       </c>
       <c r="R38" t="n">
-        <v>7099</v>
+        <v>20382</v>
       </c>
       <c r="S38" t="n">
-        <v>11743</v>
+        <v>16855</v>
       </c>
       <c r="V38" t="n">
-        <v>10219</v>
+        <v>14668</v>
       </c>
     </row>
     <row r="39">
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>104500</v>
+        <v>134100</v>
       </c>
       <c r="R39" t="n">
-        <v>10391</v>
+        <v>26667</v>
       </c>
       <c r="V39" t="n">
-        <v>8662</v>
+        <v>11116</v>
       </c>
     </row>
     <row r="40">
@@ -2914,16 +2914,16 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>47900</v>
+        <v>67500</v>
       </c>
       <c r="R40" t="n">
-        <v>4655</v>
+        <v>13119</v>
       </c>
       <c r="U40" t="n">
-        <v>9567</v>
+        <v>13482</v>
       </c>
       <c r="V40" t="n">
-        <v>9157</v>
+        <v>12904</v>
       </c>
     </row>
     <row r="41">
@@ -2972,13 +2972,13 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>83800</v>
+        <v>94700</v>
       </c>
       <c r="R41" t="n">
-        <v>8180</v>
+        <v>9243</v>
       </c>
       <c r="V41" t="n">
-        <v>6818</v>
+        <v>7705</v>
       </c>
     </row>
     <row r="42">
@@ -3027,13 +3027,13 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>176100</v>
+        <v>257700</v>
       </c>
       <c r="R42" t="n">
-        <v>35795</v>
+        <v>78573</v>
       </c>
       <c r="V42" t="n">
-        <v>14706</v>
+        <v>21521</v>
       </c>
     </row>
     <row r="43">
@@ -3079,16 +3079,16 @@
         <v>45817</v>
       </c>
       <c r="L43" t="n">
-        <v>12900</v>
+        <v>13700</v>
       </c>
       <c r="M43" t="n">
-        <v>101800</v>
+        <v>107600</v>
       </c>
       <c r="R43" t="n">
-        <v>23819</v>
+        <v>25189</v>
       </c>
       <c r="V43" t="n">
-        <v>8473</v>
+        <v>8956</v>
       </c>
     </row>
     <row r="44">
@@ -3137,16 +3137,16 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>44500</v>
+        <v>46200</v>
       </c>
       <c r="R44" t="n">
-        <v>4306</v>
+        <v>4471</v>
       </c>
       <c r="U44" t="n">
-        <v>8600</v>
+        <v>8928</v>
       </c>
       <c r="V44" t="n">
-        <v>8822</v>
+        <v>9159</v>
       </c>
     </row>
     <row r="45">
@@ -3195,16 +3195,16 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>55900</v>
+        <v>85300</v>
       </c>
       <c r="O45" t="n">
-        <v>4604</v>
+        <v>7026</v>
       </c>
       <c r="R45" t="n">
-        <v>6271</v>
+        <v>19138</v>
       </c>
       <c r="V45" t="n">
-        <v>10532</v>
+        <v>16071</v>
       </c>
     </row>
     <row r="46">
@@ -3253,13 +3253,13 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>323400</v>
+        <v>484800</v>
       </c>
       <c r="R46" t="n">
-        <v>97393</v>
+        <v>145999</v>
       </c>
       <c r="V46" t="n">
-        <v>26440</v>
+        <v>39635</v>
       </c>
     </row>
     <row r="47">
@@ -3308,19 +3308,19 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1083400</v>
+        <v>1148800</v>
       </c>
       <c r="P47" t="n">
-        <v>428123</v>
+        <v>453966</v>
       </c>
       <c r="Q47" t="n">
-        <v>277571</v>
+        <v>294326</v>
       </c>
       <c r="R47" t="n">
-        <v>173724</v>
+        <v>184211</v>
       </c>
       <c r="V47" t="n">
-        <v>133723</v>
+        <v>141795</v>
       </c>
     </row>
     <row r="48">
@@ -3369,19 +3369,19 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>715900</v>
+        <v>1116400</v>
       </c>
       <c r="P48" t="n">
-        <v>291308</v>
+        <v>454276</v>
       </c>
       <c r="Q48" t="n">
-        <v>174047</v>
+        <v>271415</v>
       </c>
       <c r="R48" t="n">
-        <v>113080</v>
+        <v>352680</v>
       </c>
       <c r="V48" t="n">
-        <v>85173</v>
+        <v>132822</v>
       </c>
     </row>
     <row r="49">
@@ -3430,16 +3430,16 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>72400</v>
+        <v>108100</v>
       </c>
       <c r="R49" t="n">
-        <v>7198</v>
+        <v>21496</v>
       </c>
       <c r="T49" t="n">
-        <v>7283</v>
+        <v>10874</v>
       </c>
       <c r="V49" t="n">
-        <v>10455</v>
+        <v>15611</v>
       </c>
     </row>
     <row r="50">

--- a/sample-data/acme-sample-50.xlsx
+++ b/sample-data/acme-sample-50.xlsx
@@ -538,22 +538,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ruth Mcneil</t>
+          <t>Harini Mishra</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ruth.mcneil.5138@acme.example</t>
+          <t>harini.mishra.2795@acme.example</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>product</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Principal Account Executive</t>
+          <t>Principal Product Manager</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>42006</v>
+        <v>42005</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>46327</v>
@@ -581,22 +581,28 @@
       <c r="M2" t="n">
         <v>-5000</v>
       </c>
+      <c r="P2" t="n">
+        <v>1518988</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1032589</v>
+      </c>
       <c r="R2" t="n">
-        <v>81893</v>
+        <v>1954616</v>
       </c>
       <c r="V2" t="n">
-        <v>22796</v>
+        <v>492364</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HR-58701</t>
+          <t>HR-96108</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ria Schleich</t>
+          <t>Anay Barad</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -606,12 +612,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Head of Design</t>
+          <t>Head of Engineering</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -619,50 +625,53 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>42011</v>
+        <v>42006</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L3" t="n">
-        <v>36200</v>
+        <v>556600</v>
       </c>
       <c r="M3" t="n">
-        <v>336000</v>
+        <v>6226185</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2384232</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1479326</v>
       </c>
       <c r="R3" t="n">
-        <v>113233</v>
-      </c>
-      <c r="U3" t="n">
-        <v>65270</v>
+        <v>3289693</v>
       </c>
       <c r="V3" t="n">
-        <v>67053</v>
+        <v>739628</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HR-72009</t>
+          <t>HR-40255</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rodney Figueroa</t>
+          <t>Ishaan Parekh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rodney.figueroa.6273@acme.example</t>
+          <t>ishaan.parekh.2525@acme.example</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -672,15 +681,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Head of Customer Support</t>
+          <t>Principal IT Engineer</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -689,54 +698,54 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>42016</v>
+        <v>42015</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L4" t="n">
-        <v>16900</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>262920</v>
-      </c>
-      <c r="N4" t="n">
-        <v>21051</v>
+        <v>3144330</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1300376</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>769882</v>
       </c>
       <c r="R4" t="n">
-        <v>89099</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50310</v>
+        <v>1529037</v>
       </c>
       <c r="V4" t="n">
-        <v>42499</v>
+        <v>373134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HR-40255</t>
+          <t>HR-22906</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ashley Bruce</t>
+          <t>Suhani Swamy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ashley.bruce.2208@acme.example</t>
+          <t>suhani.swamy.735@acme.example</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Head of Sales</t>
+          <t>Principal Financial Analyst</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -744,7 +753,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -753,7 +762,7 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>42022</v>
+        <v>42020</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>46327</v>
@@ -762,39 +771,45 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>499170</v>
+        <v>4115790</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1656944</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1040417</v>
       </c>
       <c r="R5" t="n">
-        <v>150780</v>
+        <v>2030894</v>
       </c>
       <c r="V5" t="n">
-        <v>39431</v>
+        <v>481254</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HR-22906</t>
+          <t>HR-39664</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ekiya Koshy</t>
+          <t>Lavanya Banerjee</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ekiya.koshy.99@acme.example</t>
+          <t>lavanya.banerjee.9658@acme.example</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Head of Operations</t>
+          <t>Head of Sales</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -819,56 +834,56 @@
         <v>46327</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="M6" t="n">
-        <v>4998840</v>
+        <v>3735060</v>
       </c>
       <c r="P6" t="n">
-        <v>1943115</v>
+        <v>1462797</v>
       </c>
       <c r="Q6" t="n">
-        <v>1240917</v>
+        <v>922189</v>
       </c>
       <c r="R6" t="n">
-        <v>2471098</v>
+        <v>1881807</v>
       </c>
       <c r="V6" t="n">
-        <v>598981</v>
+        <v>455218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HR-90972</t>
+          <t>HR-45196</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yauvani De</t>
+          <t>Georgina Wong</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>yauvani.de.7617@acme.example</t>
+          <t>georgina.wong.7541@acme.example</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Principal Data Scientist</t>
+          <t>Head of Marketing</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -877,54 +892,51 @@
         </is>
       </c>
       <c r="I7" s="1" t="n">
-        <v>42030</v>
+        <v>42022</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="M7" t="n">
-        <v>3619350</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1403080</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>932354</v>
+        <v>214515</v>
       </c>
       <c r="R7" t="n">
-        <v>1785986</v>
+        <v>71686</v>
+      </c>
+      <c r="T7" t="n">
+        <v>20563</v>
       </c>
       <c r="V7" t="n">
-        <v>429373</v>
+        <v>29056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HR-90972</t>
+          <t>HR-45196</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vihaan Divan</t>
+          <t>Chameli Kale</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vihaan.divan.7463@acme.example</t>
+          <t>chameli.kale.6853@acme.example</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Principal Financial Analyst</t>
+          <t>Principal Account Executive</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -937,66 +949,66 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I8" s="1" t="n">
-        <v>42034</v>
+        <v>42026</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>447200</v>
       </c>
       <c r="M8" t="n">
-        <v>4039245</v>
+        <v>3535770</v>
       </c>
       <c r="P8" t="n">
-        <v>1675338</v>
+        <v>1431296</v>
       </c>
       <c r="Q8" t="n">
-        <v>985327</v>
+        <v>889029</v>
       </c>
       <c r="R8" t="n">
-        <v>2018648</v>
+        <v>1923415</v>
       </c>
       <c r="V8" t="n">
-        <v>508065</v>
+        <v>411591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HR-18239</t>
+          <t>HR-88097</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Theodore Sethi</t>
+          <t>Glenn Collier</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>theodore.sethi.2802@acme.example</t>
+          <t>glenn.collier.3496@acme.example</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>legal</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Principal Engineer</t>
+          <t>Head of Legal</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1005,54 +1017,51 @@
         </is>
       </c>
       <c r="I9" s="1" t="n">
-        <v>42037</v>
+        <v>42027</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L9" t="n">
-        <v>478900</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4008270</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1537427</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>995568</v>
+        <v>239190</v>
       </c>
       <c r="R9" t="n">
-        <v>2021335</v>
+        <v>71194</v>
+      </c>
+      <c r="T9" t="n">
+        <v>22912</v>
       </c>
       <c r="V9" t="n">
-        <v>492222</v>
+        <v>34267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HR-17871</t>
+          <t>HR-18239</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Janice Jefferson</t>
+          <t>Yashasvi Babu</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>janice.jefferson.6789@acme.example</t>
+          <t>yashasvi.babu.7775@acme.example</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>customer-support</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Head of Customer Support</t>
+          <t>Head of Engineering</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1060,7 +1069,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1069,54 +1078,54 @@
         </is>
       </c>
       <c r="I10" s="1" t="n">
-        <v>42037</v>
+        <v>42029</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L10" t="n">
-        <v>21100</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>260085</v>
-      </c>
-      <c r="N10" t="n">
-        <v>21743</v>
+        <v>6577410</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2705007</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1662345</v>
       </c>
       <c r="R10" t="n">
-        <v>94787</v>
-      </c>
-      <c r="S10" t="n">
-        <v>51180</v>
+        <v>3420612</v>
       </c>
       <c r="V10" t="n">
-        <v>45642</v>
+        <v>797288</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HR-95332</t>
+          <t>HR-96904</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stacey Parker</t>
+          <t>Jennifer Perez</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>stacey.parker.8544@acme.example</t>
+          <t>jennifer.perez.6905@acme.example</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>customer-support</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Head of Engineering</t>
+          <t>Head of Customer Support</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1124,7 +1133,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1133,68 +1142,71 @@
         </is>
       </c>
       <c r="I11" s="1" t="n">
-        <v>42039</v>
+        <v>42037</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>21100</v>
       </c>
       <c r="M11" t="n">
-        <v>257250</v>
+        <v>260085</v>
+      </c>
+      <c r="N11" t="n">
+        <v>21743</v>
       </c>
       <c r="R11" t="n">
-        <v>78531</v>
-      </c>
-      <c r="T11" t="n">
-        <v>24919</v>
+        <v>94787</v>
+      </c>
+      <c r="S11" t="n">
+        <v>51180</v>
       </c>
       <c r="V11" t="n">
-        <v>37063</v>
+        <v>45642</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HR-67193</t>
+          <t>HR-30361</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Howard Pugh</t>
+          <t>Dayamai Dayal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>howard.pugh.2057@acme.example</t>
+          <t>dayamai.dayal.8898@acme.example</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>customer-support</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Head of Customer Support</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I12" s="1" t="n">
-        <v>42041</v>
+        <v>42037</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>46327</v>
@@ -1203,106 +1215,103 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>175665</v>
+        <v>3865470</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1607416</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>945337</v>
       </c>
       <c r="R12" t="n">
-        <v>53930</v>
-      </c>
-      <c r="T12" t="n">
-        <v>17465</v>
+        <v>1836234</v>
       </c>
       <c r="V12" t="n">
-        <v>25171</v>
+        <v>460908</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HR-36257</t>
+          <t>HR-72057</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jagat Sarraf</t>
+          <t>Patricia Chapman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jagat.sarraf.6283@acme.example</t>
+          <t>patricia.chapman.4781@acme.example</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Principal Account Executive</t>
+          <t>Head of Engineering</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I13" s="1" t="n">
-        <v>42041</v>
+        <v>42039</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L13" t="n">
-        <v>193200</v>
+        <v>70200</v>
       </c>
       <c r="M13" t="n">
-        <v>2366175</v>
-      </c>
-      <c r="P13" t="n">
-        <v>936444</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>590736</v>
+        <v>494865</v>
       </c>
       <c r="R13" t="n">
-        <v>1204044</v>
+        <v>177945</v>
       </c>
       <c r="V13" t="n">
-        <v>284735</v>
+        <v>41173</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HR-59439</t>
+          <t>HR-68177</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maud van Bruchem</t>
+          <t>Deborah Moore</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>maud.vanbruchem.9948@acme.example</t>
+          <t>deborah.moore.8810@acme.example</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>it</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Principal Engineer</t>
+          <t>Principal IT Engineer</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1310,7 +1319,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1319,7 +1328,7 @@
         </is>
       </c>
       <c r="I14" s="1" t="n">
-        <v>42041</v>
+        <v>42039</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>46327</v>
@@ -1328,42 +1337,39 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>207060</v>
-      </c>
-      <c r="O14" t="n">
-        <v>17234</v>
+        <v>362250</v>
       </c>
       <c r="R14" t="n">
-        <v>67103</v>
+        <v>108917</v>
       </c>
       <c r="V14" t="n">
-        <v>38821</v>
+        <v>27737</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HR-96777</t>
+          <t>HR-58695</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ridhi Chowdhury</t>
+          <t>Divya Kaul</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ridhi.chowdhury.7548@acme.example</t>
+          <t>divya.kaul.7126@acme.example</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Head of Marketing</t>
+          <t>Head of Engineering</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1380,7 +1386,7 @@
         </is>
       </c>
       <c r="I15" s="1" t="n">
-        <v>42044</v>
+        <v>42051</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>46327</v>
@@ -1389,45 +1395,45 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4844280</v>
+        <v>5744130</v>
       </c>
       <c r="P15" t="n">
-        <v>1953464</v>
+        <v>2404907</v>
       </c>
       <c r="Q15" t="n">
-        <v>1165839</v>
+        <v>1489580</v>
       </c>
       <c r="R15" t="n">
-        <v>2388494</v>
+        <v>2997133</v>
       </c>
       <c r="V15" t="n">
-        <v>602055</v>
+        <v>722593</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HR-72770</t>
+          <t>HR-41347</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anirudh Iyer</t>
+          <t>Ekansh Subramaniam</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>anirudh.iyer.8913@acme.example</t>
+          <t>ekansh.subramaniam.5833@acme.example</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>legal</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Principal Engineer</t>
+          <t>Principal Counsel</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1444,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" s="1" t="n">
-        <v>42044</v>
+        <v>42073</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>46327</v>
@@ -1453,45 +1459,45 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4593120</v>
+        <v>3169320</v>
       </c>
       <c r="P16" t="n">
-        <v>1887170</v>
+        <v>1300450</v>
       </c>
       <c r="Q16" t="n">
-        <v>1138258</v>
+        <v>811918</v>
       </c>
       <c r="R16" t="n">
-        <v>2347637</v>
+        <v>1604739</v>
       </c>
       <c r="V16" t="n">
-        <v>564232</v>
+        <v>365825</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HR-90809</t>
+          <t>HR-19545</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Douglas Allan</t>
+          <t>Angelina Adriaense</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>douglas.allan.9767@acme.example</t>
+          <t>angelina.adriaense.2580@acme.example</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Principal Data Scientist</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1499,129 +1505,126 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I17" s="1" t="n">
-        <v>42046</v>
+        <v>42084</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L17" t="n">
-        <v>13900</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>157290</v>
+        <v>146370</v>
+      </c>
+      <c r="O17" t="n">
+        <v>11475</v>
       </c>
       <c r="R17" t="n">
-        <v>53666</v>
-      </c>
-      <c r="T17" t="n">
-        <v>16353</v>
+        <v>47778</v>
       </c>
       <c r="V17" t="n">
-        <v>22885</v>
+        <v>25285</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HR-72057</t>
+          <t>HR-13463</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tijn Schenk</t>
+          <t>Rachael Johnson</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>tijn.schenk.5163@acme.example</t>
+          <t>rachael.johnson.3013@acme.example</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Principal Product Manager</t>
+          <t>Head of Engineering</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I18" s="1" t="n">
-        <v>42047</v>
+        <v>42091</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>52800</v>
       </c>
       <c r="M18" t="n">
-        <v>171150</v>
-      </c>
-      <c r="O18" t="n">
-        <v>14082</v>
+        <v>663390</v>
       </c>
       <c r="R18" t="n">
-        <v>55222</v>
+        <v>219589</v>
       </c>
       <c r="V18" t="n">
-        <v>30211</v>
+        <v>51340</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HR-68177</t>
+          <t>HR-38816</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Philip van Schevinghuizen</t>
+          <t>Scott Sanchez</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>philip.vanschevinghuizen.1972@acme.example</t>
+          <t>scott.sanchez.5591@acme.example</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>legal</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Head of Legal</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1630,51 +1633,48 @@
         </is>
       </c>
       <c r="I19" s="1" t="n">
-        <v>42048</v>
+        <v>42100</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L19" t="n">
-        <v>25700</v>
+        <v>17100</v>
       </c>
       <c r="M19" t="n">
-        <v>258825</v>
-      </c>
-      <c r="O19" t="n">
-        <v>20465</v>
+        <v>263340</v>
       </c>
       <c r="R19" t="n">
-        <v>90807</v>
+        <v>88061</v>
       </c>
       <c r="V19" t="n">
-        <v>48216</v>
+        <v>20475</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HR-55040</t>
+          <t>HR-93347</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guiseppe Winkler</t>
+          <t>William Garcia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>guiseppe.winkler.2349@acme.example</t>
+          <t>william.garcia.431@acme.example</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>product</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Principal Designer</t>
+          <t>Principal Product Manager</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1691,51 +1691,48 @@
         </is>
       </c>
       <c r="I20" s="1" t="n">
-        <v>42055</v>
+        <v>42111</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L20" t="n">
-        <v>14500</v>
+        <v>33400</v>
       </c>
       <c r="M20" t="n">
-        <v>147000</v>
+        <v>326655</v>
       </c>
       <c r="R20" t="n">
-        <v>48230</v>
-      </c>
-      <c r="U20" t="n">
-        <v>28347</v>
+        <v>110119</v>
       </c>
       <c r="V20" t="n">
-        <v>30129</v>
+        <v>26251</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HR-28378</t>
+          <t>HR-16650</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brian Elliott</t>
+          <t>Apostolos Zahn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>brian.elliott.4579@acme.example</t>
+          <t>apostolos.zahn.4265@acme.example</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Principal Engineer</t>
+          <t>Principal Account Executive</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1743,7 +1740,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1752,48 +1749,51 @@
         </is>
       </c>
       <c r="I21" s="1" t="n">
-        <v>42069</v>
+        <v>42111</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>21300</v>
       </c>
       <c r="M21" t="n">
-        <v>361830</v>
+        <v>166635</v>
       </c>
       <c r="R21" t="n">
-        <v>112712</v>
+        <v>59379</v>
+      </c>
+      <c r="U21" t="n">
+        <v>34402</v>
       </c>
       <c r="V21" t="n">
-        <v>29285</v>
+        <v>31753</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HR-68458</t>
+          <t>HR-18786</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ikbal Luthra</t>
+          <t>Mekhala Viswanathan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ikbal.luthra.4856@acme.example</t>
+          <t>mekhala.viswanathan.4990@acme.example</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>data</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Head of Sales</t>
+          <t>Head of Data</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1806,11 +1806,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I22" s="1" t="n">
-        <v>42069</v>
+        <v>42112</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>46327</v>
@@ -1819,45 +1819,45 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6069000</v>
+        <v>5554710</v>
       </c>
       <c r="P22" t="n">
-        <v>2436058</v>
+        <v>2251616</v>
       </c>
       <c r="Q22" t="n">
-        <v>1455023</v>
+        <v>1425455</v>
       </c>
       <c r="R22" t="n">
-        <v>3070522</v>
+        <v>2895454</v>
       </c>
       <c r="V22" t="n">
-        <v>697825</v>
+        <v>680964</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HR-28147</t>
+          <t>HR-81135</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jason Clark</t>
+          <t>Chanchal Guha</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jason.clark.1000@acme.example</t>
+          <t>chanchal.guha.3638@acme.example</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>customer-support</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Head of Finance</t>
+          <t>Head of Customer Support</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1865,67 +1865,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I23" s="1" t="n">
-        <v>42071</v>
+        <v>42113</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L23" t="n">
-        <v>53500</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>433755</v>
-      </c>
-      <c r="N23" t="n">
-        <v>34716</v>
+        <v>3773910</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1577492</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>902035</v>
       </c>
       <c r="R23" t="n">
-        <v>149772</v>
-      </c>
-      <c r="S23" t="n">
-        <v>86030</v>
+        <v>1854994</v>
       </c>
       <c r="V23" t="n">
-        <v>71859</v>
+        <v>446772</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HR-93543</t>
+          <t>HR-91424</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Anmol Din</t>
+          <t>Oliver Shere</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>anmol.din.4613@acme.example</t>
+          <t>oliver.shere.5836@acme.example</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Principal Financial Analyst</t>
+          <t>Head of Engineering</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1938,44 +1938,44 @@
         </is>
       </c>
       <c r="I24" s="1" t="n">
-        <v>42073</v>
+        <v>42114</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L24" t="n">
-        <v>173100</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1627710</v>
+        <v>5515125</v>
       </c>
       <c r="P24" t="n">
-        <v>680436</v>
+        <v>2140958</v>
       </c>
       <c r="Q24" t="n">
-        <v>426801</v>
+        <v>1370447</v>
       </c>
       <c r="R24" t="n">
-        <v>906879</v>
+        <v>2744189</v>
       </c>
       <c r="V24" t="n">
-        <v>199721</v>
+        <v>665535</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HR-35944</t>
+          <t>HR-17803</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Feline van Dam</t>
+          <t>Abeer Devan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>feline.vandam.786@acme.example</t>
+          <t>abeer.devan.3091@acme.example</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1993,16 +1993,16 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I25" s="1" t="n">
-        <v>42077</v>
+        <v>42122</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>46327</v>
@@ -2011,42 +2011,45 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>264390</v>
-      </c>
-      <c r="O25" t="n">
-        <v>21596</v>
+        <v>5039265</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1921703</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1239778</v>
       </c>
       <c r="R25" t="n">
-        <v>88908</v>
+        <v>2516697</v>
       </c>
       <c r="V25" t="n">
-        <v>46359</v>
+        <v>584765</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HR-38816</t>
+          <t>HR-65830</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Akshay Khatri</t>
+          <t>Donald Guerra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>akshay.khatri.898@acme.example</t>
+          <t>donald.guerra.9160@acme.example</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>product</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Principal Financial Analyst</t>
+          <t>Principal Product Manager</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2054,7 +2057,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2063,7 +2066,7 @@
         </is>
       </c>
       <c r="I26" s="1" t="n">
-        <v>42079</v>
+        <v>42122</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>46327</v>
@@ -2072,117 +2075,105 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3665550</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1393608</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>873492</v>
+        <v>305445</v>
       </c>
       <c r="R26" t="n">
-        <v>1858515</v>
+        <v>88927</v>
       </c>
       <c r="V26" t="n">
-        <v>435393</v>
+        <v>25452</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HR-45043</t>
+          <t>HR-40940</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zehaan Bhatti</t>
+          <t>Mary Wright</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>zehaan.bhatti.7595@acme.example</t>
+          <t>mary.wright.5243@acme.example</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>product</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Principal Engineer</t>
+          <t>Head of Product</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I27" s="1" t="n">
-        <v>42080</v>
+        <v>42124</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L27" t="n">
-        <v>426900</v>
+        <v>45700</v>
       </c>
       <c r="M27" t="n">
-        <v>4477620</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1763705</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1079225</v>
+        <v>469245</v>
       </c>
       <c r="R27" t="n">
-        <v>2406915</v>
+        <v>158806</v>
       </c>
       <c r="V27" t="n">
-        <v>547733</v>
+        <v>36100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HR-78094</t>
+          <t>HR-16601</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Liselotte Hermann</t>
+          <t>Ellie Lee</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>liselotte.hermann.6135@acme.example</t>
+          <t>ellie.lee.287@acme.example</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>product</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Principal Marketing Specialist</t>
+          <t>Head of Product</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,51 +2182,51 @@
         </is>
       </c>
       <c r="I28" s="1" t="n">
-        <v>42082</v>
+        <v>42135</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L28" t="n">
-        <v>19700</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>141330</v>
+        <v>195825</v>
       </c>
       <c r="R28" t="n">
-        <v>48535</v>
-      </c>
-      <c r="U28" t="n">
-        <v>28170</v>
+        <v>60604</v>
+      </c>
+      <c r="T28" t="n">
+        <v>19879</v>
       </c>
       <c r="V28" t="n">
-        <v>27372</v>
+        <v>27265</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HR-39498</t>
+          <t>HR-26481</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brandon Ellis</t>
+          <t>Liesbeth Bärer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>brandon.ellis.3026@acme.example</t>
+          <t>liesbeth.barer.5910@acme.example</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Principal Account Executive</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2243,50 +2234,50 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I29" s="1" t="n">
-        <v>42083</v>
+        <v>42137</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L29" t="n">
-        <v>15500</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>138810</v>
+        <v>193725</v>
       </c>
       <c r="R29" t="n">
-        <v>46683</v>
-      </c>
-      <c r="T29" t="n">
-        <v>14391</v>
+        <v>55431</v>
+      </c>
+      <c r="U29" t="n">
+        <v>36830</v>
       </c>
       <c r="V29" t="n">
-        <v>18872</v>
+        <v>39281</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HR-72313</t>
+          <t>HR-17818</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Luke Sundaram</t>
+          <t>Stuart Davies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>luke.sundaram.6245@acme.example</t>
+          <t>stuart.davies.321@acme.example</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2296,15 +2287,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Head of Engineering</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,62 +2304,59 @@
         </is>
       </c>
       <c r="I30" s="1" t="n">
-        <v>42083</v>
+        <v>42141</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="L30" t="n">
-        <v>324500</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>5409915</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2187003</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1324505</v>
+        <v>145005</v>
       </c>
       <c r="R30" t="n">
-        <v>2699616</v>
+        <v>41764</v>
+      </c>
+      <c r="T30" t="n">
+        <v>14466</v>
       </c>
       <c r="V30" t="n">
-        <v>656486</v>
+        <v>20067</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HR-16650</t>
+          <t>HR-52996</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dave Takkelenburg</t>
+          <t>Herbert Rohleder</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dave.takkelenburg.6250@acme.example</t>
+          <t>herbert.rohleder.6390@acme.example</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>customer-support</t>
+          <t>it</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Principal Support Specialist</t>
+          <t>Head of IT</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2377,7 +2365,7 @@
         </is>
       </c>
       <c r="I31" s="1" t="n">
-        <v>42093</v>
+        <v>42144</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>46327</v>
@@ -2386,16 +2374,16 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>97020</v>
-      </c>
-      <c r="O31" t="n">
-        <v>7979</v>
+        <v>258405</v>
       </c>
       <c r="R31" t="n">
-        <v>31112</v>
+        <v>73779</v>
+      </c>
+      <c r="U31" t="n">
+        <v>51986</v>
       </c>
       <c r="V31" t="n">
-        <v>16949</v>
+        <v>49190</v>
       </c>
     </row>
     <row r="32">
@@ -2583,12 +2571,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Isaac Dewan</t>
+          <t>Denise Walker</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>isaac.dewan.15004@acme.example</t>
+          <t>denise.walker.15004@acme.example</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2598,42 +2586,36 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I35" s="1" t="n">
-        <v>45775</v>
+        <v>46143</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>948400</v>
-      </c>
-      <c r="P35" t="n">
-        <v>376407</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>226751</v>
+        <v>158500</v>
       </c>
       <c r="R35" t="n">
-        <v>147576</v>
+        <v>30912</v>
       </c>
       <c r="V35" t="n">
-        <v>116320</v>
+        <v>12747</v>
       </c>
     </row>
     <row r="36">
@@ -2644,51 +2626,54 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Donald Walker</t>
+          <t>Maja Heere</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>donald.walker.15005@acme.example</t>
+          <t>maja.heere.15005@acme.example</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>customer-support</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Principal Support Specialist</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I36" s="1" t="n">
-        <v>45546</v>
+        <v>44791</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>15700</v>
       </c>
       <c r="M36" t="n">
-        <v>89800</v>
+        <v>139800</v>
+      </c>
+      <c r="O36" t="n">
+        <v>10847</v>
       </c>
       <c r="R36" t="n">
-        <v>9356</v>
+        <v>51993</v>
       </c>
       <c r="V36" t="n">
-        <v>7255</v>
+        <v>25413</v>
       </c>
     </row>
     <row r="37">
@@ -2699,57 +2684,54 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charan Chahal</t>
+          <t>Mandy Dowerg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>charan.chahal.15006@acme.example</t>
+          <t>mandy.dowerg.15006@acme.example</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Associate Operations Analyst</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I37" s="1" t="n">
-        <v>46200</v>
+        <v>44476</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>899900</v>
-      </c>
-      <c r="P37" t="n">
-        <v>361753</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>219689</v>
+        <v>69900</v>
       </c>
       <c r="R37" t="n">
-        <v>143707</v>
+        <v>13803</v>
+      </c>
+      <c r="U37" t="n">
+        <v>13839</v>
       </c>
       <c r="V37" t="n">
-        <v>105955</v>
+        <v>14539</v>
       </c>
     </row>
     <row r="38">
@@ -2770,20 +2752,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>customer-support</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Senior Support Specialist</t>
+          <t>Lead Account Executive</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2792,25 +2774,19 @@
         </is>
       </c>
       <c r="I38" s="1" t="n">
-        <v>45055</v>
+        <v>44373</v>
       </c>
       <c r="L38" t="n">
-        <v>10200</v>
+        <v>19900</v>
       </c>
       <c r="M38" t="n">
-        <v>84400</v>
-      </c>
-      <c r="N38" t="n">
-        <v>6914</v>
+        <v>191400</v>
       </c>
       <c r="R38" t="n">
-        <v>20382</v>
-      </c>
-      <c r="S38" t="n">
-        <v>16855</v>
+        <v>42932</v>
       </c>
       <c r="V38" t="n">
-        <v>14668</v>
+        <v>15089</v>
       </c>
     </row>
     <row r="39">
@@ -2821,51 +2797,57 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stephanie Miller</t>
+          <t>Isaac Dewan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>stephanie.miller.15008@acme.example</t>
+          <t>isaac.dewan.15008@acme.example</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>customer-support</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Associate Support Specialist</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I39" s="1" t="n">
-        <v>45296</v>
+        <v>45915</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>77700</v>
       </c>
       <c r="M39" t="n">
-        <v>134100</v>
+        <v>594400</v>
+      </c>
+      <c r="P39" t="n">
+        <v>246223</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>142625</v>
       </c>
       <c r="R39" t="n">
-        <v>26667</v>
+        <v>103298</v>
       </c>
       <c r="V39" t="n">
-        <v>11116</v>
+        <v>70660</v>
       </c>
     </row>
     <row r="40">
@@ -2876,26 +2858,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marcus Dowerg</t>
+          <t>Alida Weihmann</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>marcus.dowerg.15009@acme.example</t>
+          <t>alida.weihmann.15009@acme.example</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>it</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lead Operations Analyst</t>
+          <t>Associate IT Engineer</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2904,26 +2886,26 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I40" s="1" t="n">
-        <v>44880</v>
+        <v>45585</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="M40" t="n">
-        <v>67500</v>
+        <v>47500</v>
       </c>
       <c r="R40" t="n">
-        <v>13119</v>
+        <v>5106</v>
       </c>
       <c r="U40" t="n">
-        <v>13482</v>
+        <v>9478</v>
       </c>
       <c r="V40" t="n">
-        <v>12904</v>
+        <v>9079</v>
       </c>
     </row>
     <row r="41">
@@ -2934,51 +2916,54 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Javier Johnson</t>
+          <t>Emmy Henschel</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>javier.johnson.15010@acme.example</t>
+          <t>emmy.henschel.15010@acme.example</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Associate IT Engineer</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I41" s="1" t="n">
-        <v>45237</v>
+        <v>42987</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>94700</v>
+        <v>169800</v>
       </c>
       <c r="R41" t="n">
-        <v>9243</v>
+        <v>50004</v>
+      </c>
+      <c r="U41" t="n">
+        <v>34543</v>
       </c>
       <c r="V41" t="n">
-        <v>7705</v>
+        <v>34815</v>
       </c>
     </row>
     <row r="42">
@@ -2989,51 +2974,54 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Daniel Wagner</t>
+          <t>Amelia Schellekens</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>daniel.wagner.15011@acme.example</t>
+          <t>amelia.schellekens.15011@acme.example</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>design</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Principal Account Executive</t>
+          <t>Lead Designer</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I42" s="1" t="n">
-        <v>44318</v>
+        <v>44594</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="M42" t="n">
-        <v>257700</v>
+        <v>118800</v>
+      </c>
+      <c r="O42" t="n">
+        <v>9839</v>
       </c>
       <c r="R42" t="n">
-        <v>78573</v>
+        <v>27776</v>
       </c>
       <c r="V42" t="n">
-        <v>21521</v>
+        <v>22088</v>
       </c>
     </row>
     <row r="43">
@@ -3044,22 +3032,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alyssa Gonzalez</t>
+          <t>Charan Chahal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>alyssa.gonzalez.15012@acme.example</t>
+          <t>charan.chahal.15012@acme.example</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>customer-support</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Senior Support Specialist</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -3067,28 +3055,34 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I43" s="1" t="n">
-        <v>45817</v>
+        <v>44366</v>
       </c>
       <c r="L43" t="n">
-        <v>13700</v>
+        <v>130600</v>
       </c>
       <c r="M43" t="n">
-        <v>107600</v>
+        <v>1510500</v>
+      </c>
+      <c r="P43" t="n">
+        <v>630367</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>395456</v>
       </c>
       <c r="R43" t="n">
-        <v>25189</v>
+        <v>536579</v>
       </c>
       <c r="V43" t="n">
-        <v>8956</v>
+        <v>188052</v>
       </c>
     </row>
     <row r="44">
@@ -3099,22 +3093,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alida Weihmann</t>
+          <t>Dorit Etzold</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>alida.weihmann.15013@acme.example</t>
+          <t>dorit.etzold.15013@acme.example</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Associate Account Executive</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -3131,22 +3125,22 @@
         </is>
       </c>
       <c r="I44" s="1" t="n">
-        <v>45855</v>
+        <v>46234</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>46200</v>
+        <v>54400</v>
       </c>
       <c r="R44" t="n">
-        <v>4471</v>
+        <v>5181</v>
       </c>
       <c r="U44" t="n">
-        <v>8928</v>
+        <v>11201</v>
       </c>
       <c r="V44" t="n">
-        <v>9159</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="45">
@@ -3157,54 +3151,57 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Maja Heere</t>
+          <t>Siddharth Balay</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>maja.heere.15014@acme.example</t>
+          <t>siddharth.balay.15014@acme.example</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>legal</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Senior Financial Analyst</t>
+          <t>Counsel</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="I45" s="1" t="n">
-        <v>44871</v>
+        <v>45611</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>85300</v>
-      </c>
-      <c r="O45" t="n">
-        <v>7026</v>
+        <v>919700</v>
+      </c>
+      <c r="P45" t="n">
+        <v>385694</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>221088</v>
       </c>
       <c r="R45" t="n">
-        <v>19138</v>
+        <v>157327</v>
       </c>
       <c r="V45" t="n">
-        <v>16071</v>
+        <v>112426</v>
       </c>
     </row>
     <row r="46">
@@ -3215,30 +3212,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Marie Gardner</t>
+          <t>Frances Griffiths</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>marie.gardner.15015@acme.example</t>
+          <t>frances.griffiths.15015@acme.example</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Head of Operations</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3247,19 +3244,22 @@
         </is>
       </c>
       <c r="I46" s="1" t="n">
-        <v>44179</v>
+        <v>44576</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="M46" t="n">
-        <v>484800</v>
+        <v>154700</v>
       </c>
       <c r="R46" t="n">
-        <v>145999</v>
+        <v>46856</v>
+      </c>
+      <c r="T46" t="n">
+        <v>15649</v>
       </c>
       <c r="V46" t="n">
-        <v>39635</v>
+        <v>21196</v>
       </c>
     </row>
     <row r="47">
@@ -3270,26 +3270,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Siddharth Balay</t>
+          <t>Amruta Chander</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>siddharth.balay.15016@acme.example</t>
+          <t>amruta.chander.15016@acme.example</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HR Partner</t>
+          <t>Principal Engineer</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3298,29 +3298,29 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I47" s="1" t="n">
-        <v>45749</v>
+        <v>42807</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1148800</v>
+        <v>2567700</v>
       </c>
       <c r="P47" t="n">
-        <v>453966</v>
+        <v>1044827</v>
       </c>
       <c r="Q47" t="n">
-        <v>294326</v>
+        <v>624249</v>
       </c>
       <c r="R47" t="n">
-        <v>184211</v>
+        <v>1216738</v>
       </c>
       <c r="V47" t="n">
-        <v>141795</v>
+        <v>305488</v>
       </c>
     </row>
     <row r="48">
@@ -3331,26 +3331,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alexander Chander</t>
+          <t>Janani Kaul</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>alexander.chander.15017@acme.example</t>
+          <t>janani.kaul.15017@acme.example</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>data</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Head of Data</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3359,29 +3359,29 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="I48" s="1" t="n">
-        <v>44287</v>
+        <v>45810</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1116400</v>
+        <v>4224900</v>
       </c>
       <c r="P48" t="n">
-        <v>454276</v>
+        <v>1699918</v>
       </c>
       <c r="Q48" t="n">
-        <v>271415</v>
+        <v>1036928</v>
       </c>
       <c r="R48" t="n">
-        <v>352680</v>
+        <v>2173496</v>
       </c>
       <c r="V48" t="n">
-        <v>132822</v>
+        <v>504246</v>
       </c>
     </row>
     <row r="49">
@@ -3392,22 +3392,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stanley Griffiths</t>
+          <t>Paul Dobes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>stanley.griffiths.15018@acme.example</t>
+          <t>paul.dobes.15018@acme.example</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lead Engineer</t>
+          <t>Lead Account Executive</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3424,22 +3424,22 @@
         </is>
       </c>
       <c r="I49" s="1" t="n">
-        <v>45079</v>
+        <v>46125</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="M49" t="n">
-        <v>108100</v>
+        <v>90200</v>
       </c>
       <c r="R49" t="n">
-        <v>21496</v>
-      </c>
-      <c r="T49" t="n">
-        <v>10874</v>
+        <v>19603</v>
+      </c>
+      <c r="U49" t="n">
+        <v>17254</v>
       </c>
       <c r="V49" t="n">
-        <v>15611</v>
+        <v>17888</v>
       </c>
     </row>
     <row r="50">
@@ -3450,26 +3450,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ikbal Kaul</t>
+          <t>Zayyan Bala</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ikbal.kaul.15019@acme.example</t>
+          <t>zayyan.bala.15019@acme.example</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>data</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3482,25 +3482,25 @@
         </is>
       </c>
       <c r="I50" s="1" t="n">
-        <v>46231</v>
+        <v>45805</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1191900</v>
+        <v>1316200</v>
       </c>
       <c r="P50" t="n">
-        <v>465876</v>
+        <v>531916</v>
       </c>
       <c r="Q50" t="n">
-        <v>292603</v>
+        <v>319854</v>
       </c>
       <c r="R50" t="n">
-        <v>186539</v>
+        <v>429445</v>
       </c>
       <c r="V50" t="n">
-        <v>141706</v>
+        <v>152654</v>
       </c>
     </row>
     <row r="51">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Connie Lawrence</t>
+          <t>Ira Saini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>connie.lawrence.15020@acme.example</t>
+          <t>ira.saini.15020@acme.example</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,19 +3543,25 @@
         </is>
       </c>
       <c r="I51" s="1" t="n">
-        <v>46156</v>
+        <v>45133</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>129100</v>
+        <v>977100</v>
+      </c>
+      <c r="P51" t="n">
+        <v>384489</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>253549</v>
       </c>
       <c r="R51" t="n">
-        <v>13141</v>
+        <v>165536</v>
       </c>
       <c r="V51" t="n">
-        <v>10229</v>
+        <v>112000</v>
       </c>
     </row>
   </sheetData>

--- a/sample-data/acme-sample-50.xlsx
+++ b/sample-data/acme-sample-50.xlsx
@@ -582,16 +582,16 @@
         <v>-5000</v>
       </c>
       <c r="P2" t="n">
-        <v>1518988</v>
+        <v>1535190</v>
       </c>
       <c r="Q2" t="n">
-        <v>1032589</v>
+        <v>1043603</v>
       </c>
       <c r="R2" t="n">
-        <v>1954616</v>
+        <v>1975465</v>
       </c>
       <c r="V2" t="n">
-        <v>492364</v>
+        <v>497616</v>
       </c>
     </row>
     <row r="3">
@@ -643,19 +643,19 @@
         <v>556600</v>
       </c>
       <c r="M3" t="n">
-        <v>6226185</v>
+        <v>6244567</v>
       </c>
       <c r="P3" t="n">
-        <v>2384232</v>
+        <v>2391271</v>
       </c>
       <c r="Q3" t="n">
-        <v>1479326</v>
+        <v>1483694</v>
       </c>
       <c r="R3" t="n">
-        <v>3289693</v>
+        <v>3299405</v>
       </c>
       <c r="V3" t="n">
-        <v>739628</v>
+        <v>741812</v>
       </c>
     </row>
     <row r="4">
@@ -707,19 +707,19 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3144330</v>
+        <v>3129357</v>
       </c>
       <c r="P4" t="n">
-        <v>1300376</v>
+        <v>1294183</v>
       </c>
       <c r="Q4" t="n">
-        <v>769882</v>
+        <v>766216</v>
       </c>
       <c r="R4" t="n">
-        <v>1529037</v>
+        <v>1521756</v>
       </c>
       <c r="V4" t="n">
-        <v>373134</v>
+        <v>371357</v>
       </c>
     </row>
     <row r="5">
@@ -771,19 +771,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4115790</v>
+        <v>4165571</v>
       </c>
       <c r="P5" t="n">
-        <v>1656944</v>
+        <v>1676985</v>
       </c>
       <c r="Q5" t="n">
-        <v>1040417</v>
+        <v>1053001</v>
       </c>
       <c r="R5" t="n">
-        <v>2030894</v>
+        <v>2055458</v>
       </c>
       <c r="V5" t="n">
-        <v>481254</v>
+        <v>487075</v>
       </c>
     </row>
     <row r="6">
@@ -837,19 +837,19 @@
         <v>230000</v>
       </c>
       <c r="M6" t="n">
-        <v>3735060</v>
+        <v>3721187</v>
       </c>
       <c r="P6" t="n">
-        <v>1462797</v>
+        <v>1457364</v>
       </c>
       <c r="Q6" t="n">
-        <v>922189</v>
+        <v>918763</v>
       </c>
       <c r="R6" t="n">
-        <v>1881807</v>
+        <v>1874817</v>
       </c>
       <c r="V6" t="n">
-        <v>455218</v>
+        <v>453527</v>
       </c>
     </row>
     <row r="7">
@@ -901,16 +901,16 @@
         <v>19900</v>
       </c>
       <c r="M7" t="n">
-        <v>214515</v>
+        <v>218662</v>
       </c>
       <c r="R7" t="n">
-        <v>71686</v>
+        <v>73072</v>
       </c>
       <c r="T7" t="n">
-        <v>20563</v>
+        <v>20961</v>
       </c>
       <c r="V7" t="n">
-        <v>29056</v>
+        <v>29617</v>
       </c>
     </row>
     <row r="8">
@@ -962,19 +962,19 @@
         <v>447200</v>
       </c>
       <c r="M8" t="n">
-        <v>3535770</v>
+        <v>3579546</v>
       </c>
       <c r="P8" t="n">
-        <v>1431296</v>
+        <v>1449017</v>
       </c>
       <c r="Q8" t="n">
-        <v>889029</v>
+        <v>900036</v>
       </c>
       <c r="R8" t="n">
-        <v>1923415</v>
+        <v>1947229</v>
       </c>
       <c r="V8" t="n">
-        <v>411591</v>
+        <v>416686</v>
       </c>
     </row>
     <row r="9">
@@ -1026,16 +1026,16 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>239190</v>
+        <v>240648</v>
       </c>
       <c r="R9" t="n">
-        <v>71194</v>
+        <v>71628</v>
       </c>
       <c r="T9" t="n">
-        <v>22912</v>
+        <v>23052</v>
       </c>
       <c r="V9" t="n">
-        <v>34267</v>
+        <v>34476</v>
       </c>
     </row>
     <row r="10">
@@ -1087,19 +1087,19 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6577410</v>
+        <v>6762830</v>
       </c>
       <c r="P10" t="n">
-        <v>2705007</v>
+        <v>2781262</v>
       </c>
       <c r="Q10" t="n">
-        <v>1662345</v>
+        <v>1709208</v>
       </c>
       <c r="R10" t="n">
-        <v>3420612</v>
+        <v>3517041</v>
       </c>
       <c r="V10" t="n">
-        <v>797288</v>
+        <v>819764</v>
       </c>
     </row>
     <row r="11">
@@ -1151,19 +1151,19 @@
         <v>21100</v>
       </c>
       <c r="M11" t="n">
-        <v>260085</v>
+        <v>256122</v>
       </c>
       <c r="N11" t="n">
-        <v>21743</v>
+        <v>21412</v>
       </c>
       <c r="R11" t="n">
-        <v>94787</v>
+        <v>93342</v>
       </c>
       <c r="S11" t="n">
-        <v>51180</v>
+        <v>50400</v>
       </c>
       <c r="V11" t="n">
-        <v>45642</v>
+        <v>44947</v>
       </c>
     </row>
     <row r="12">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3865470</v>
+        <v>3962659</v>
       </c>
       <c r="P12" t="n">
-        <v>1607416</v>
+        <v>1647831</v>
       </c>
       <c r="Q12" t="n">
-        <v>945337</v>
+        <v>969106</v>
       </c>
       <c r="R12" t="n">
-        <v>1836234</v>
+        <v>1882402</v>
       </c>
       <c r="V12" t="n">
-        <v>460908</v>
+        <v>472497</v>
       </c>
     </row>
     <row r="13">
@@ -1279,13 +1279,13 @@
         <v>70200</v>
       </c>
       <c r="M13" t="n">
-        <v>494865</v>
+        <v>488125</v>
       </c>
       <c r="R13" t="n">
-        <v>177945</v>
+        <v>175521</v>
       </c>
       <c r="V13" t="n">
-        <v>41173</v>
+        <v>40612</v>
       </c>
     </row>
     <row r="14">
@@ -1337,13 +1337,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>362250</v>
+        <v>367046</v>
       </c>
       <c r="R14" t="n">
-        <v>108917</v>
+        <v>110358</v>
       </c>
       <c r="V14" t="n">
-        <v>27737</v>
+        <v>28104</v>
       </c>
     </row>
     <row r="15">
@@ -1395,19 +1395,19 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5744130</v>
+        <v>5746318</v>
       </c>
       <c r="P15" t="n">
-        <v>2404907</v>
+        <v>2405824</v>
       </c>
       <c r="Q15" t="n">
-        <v>1489580</v>
+        <v>1490148</v>
       </c>
       <c r="R15" t="n">
-        <v>2997133</v>
+        <v>2998274</v>
       </c>
       <c r="V15" t="n">
-        <v>722593</v>
+        <v>722868</v>
       </c>
     </row>
     <row r="16">
@@ -1459,19 +1459,19 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3169320</v>
+        <v>3197995</v>
       </c>
       <c r="P16" t="n">
-        <v>1300450</v>
+        <v>1312216</v>
       </c>
       <c r="Q16" t="n">
-        <v>811918</v>
+        <v>819264</v>
       </c>
       <c r="R16" t="n">
-        <v>1604739</v>
+        <v>1619258</v>
       </c>
       <c r="V16" t="n">
-        <v>365825</v>
+        <v>369135</v>
       </c>
     </row>
     <row r="17">
@@ -1523,16 +1523,16 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>146370</v>
+        <v>147694</v>
       </c>
       <c r="O17" t="n">
-        <v>11475</v>
+        <v>11579</v>
       </c>
       <c r="R17" t="n">
-        <v>47778</v>
+        <v>48210</v>
       </c>
       <c r="V17" t="n">
-        <v>25285</v>
+        <v>25514</v>
       </c>
     </row>
     <row r="18">
@@ -1584,13 +1584,13 @@
         <v>52800</v>
       </c>
       <c r="M18" t="n">
-        <v>663390</v>
+        <v>667054</v>
       </c>
       <c r="R18" t="n">
-        <v>219589</v>
+        <v>220802</v>
       </c>
       <c r="V18" t="n">
-        <v>51340</v>
+        <v>51623</v>
       </c>
     </row>
     <row r="19">
@@ -1642,13 +1642,13 @@
         <v>17100</v>
       </c>
       <c r="M19" t="n">
-        <v>263340</v>
+        <v>270187</v>
       </c>
       <c r="R19" t="n">
-        <v>88061</v>
+        <v>90351</v>
       </c>
       <c r="V19" t="n">
-        <v>20475</v>
+        <v>21007</v>
       </c>
     </row>
     <row r="20">
@@ -1700,13 +1700,13 @@
         <v>33400</v>
       </c>
       <c r="M20" t="n">
-        <v>326655</v>
+        <v>334650</v>
       </c>
       <c r="R20" t="n">
-        <v>110119</v>
+        <v>112814</v>
       </c>
       <c r="V20" t="n">
-        <v>26251</v>
+        <v>26894</v>
       </c>
     </row>
     <row r="21">
@@ -1758,16 +1758,16 @@
         <v>21300</v>
       </c>
       <c r="M21" t="n">
-        <v>166635</v>
+        <v>165381</v>
       </c>
       <c r="R21" t="n">
-        <v>59379</v>
+        <v>58932</v>
       </c>
       <c r="U21" t="n">
-        <v>34402</v>
+        <v>34143</v>
       </c>
       <c r="V21" t="n">
-        <v>31753</v>
+        <v>31514</v>
       </c>
     </row>
     <row r="22">
@@ -1819,19 +1819,19 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5554710</v>
+        <v>5671623</v>
       </c>
       <c r="P22" t="n">
-        <v>2251616</v>
+        <v>2299007</v>
       </c>
       <c r="Q22" t="n">
-        <v>1425455</v>
+        <v>1455457</v>
       </c>
       <c r="R22" t="n">
-        <v>2895454</v>
+        <v>2956396</v>
       </c>
       <c r="V22" t="n">
-        <v>680964</v>
+        <v>695297</v>
       </c>
     </row>
     <row r="23">
@@ -1883,19 +1883,19 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3773910</v>
+        <v>3717840</v>
       </c>
       <c r="P23" t="n">
-        <v>1577492</v>
+        <v>1554055</v>
       </c>
       <c r="Q23" t="n">
-        <v>902035</v>
+        <v>888633</v>
       </c>
       <c r="R23" t="n">
-        <v>1854994</v>
+        <v>1827434</v>
       </c>
       <c r="V23" t="n">
-        <v>446772</v>
+        <v>440134</v>
       </c>
     </row>
     <row r="24">
@@ -1947,19 +1947,19 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5515125</v>
+        <v>5546115</v>
       </c>
       <c r="P24" t="n">
-        <v>2140958</v>
+        <v>2152989</v>
       </c>
       <c r="Q24" t="n">
-        <v>1370447</v>
+        <v>1378148</v>
       </c>
       <c r="R24" t="n">
-        <v>2744189</v>
+        <v>2759608</v>
       </c>
       <c r="V24" t="n">
-        <v>665535</v>
+        <v>669275</v>
       </c>
     </row>
     <row r="25">
@@ -2011,19 +2011,19 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5039265</v>
+        <v>5133331</v>
       </c>
       <c r="P25" t="n">
-        <v>1921703</v>
+        <v>1957574</v>
       </c>
       <c r="Q25" t="n">
-        <v>1239778</v>
+        <v>1262921</v>
       </c>
       <c r="R25" t="n">
-        <v>2516697</v>
+        <v>2563675</v>
       </c>
       <c r="V25" t="n">
-        <v>584765</v>
+        <v>595681</v>
       </c>
     </row>
     <row r="26">
@@ -2075,13 +2075,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>305445</v>
+        <v>312398</v>
       </c>
       <c r="R26" t="n">
-        <v>88927</v>
+        <v>90951</v>
       </c>
       <c r="V26" t="n">
-        <v>25452</v>
+        <v>26031</v>
       </c>
     </row>
     <row r="27">
@@ -2133,13 +2133,13 @@
         <v>45700</v>
       </c>
       <c r="M27" t="n">
-        <v>469245</v>
+        <v>477110</v>
       </c>
       <c r="R27" t="n">
-        <v>158806</v>
+        <v>161468</v>
       </c>
       <c r="V27" t="n">
-        <v>36100</v>
+        <v>36705</v>
       </c>
     </row>
     <row r="28">
@@ -2191,16 +2191,16 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>195825</v>
+        <v>200469</v>
       </c>
       <c r="R28" t="n">
-        <v>60604</v>
+        <v>62041</v>
       </c>
       <c r="T28" t="n">
-        <v>19879</v>
+        <v>20350</v>
       </c>
       <c r="V28" t="n">
-        <v>27265</v>
+        <v>27912</v>
       </c>
     </row>
     <row r="29">
@@ -2252,16 +2252,16 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>193725</v>
+        <v>191917</v>
       </c>
       <c r="R29" t="n">
-        <v>55431</v>
+        <v>54913</v>
       </c>
       <c r="U29" t="n">
-        <v>36830</v>
+        <v>36486</v>
       </c>
       <c r="V29" t="n">
-        <v>39281</v>
+        <v>38914</v>
       </c>
     </row>
     <row r="30">
@@ -2313,16 +2313,16 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>145005</v>
+        <v>148043</v>
       </c>
       <c r="R30" t="n">
-        <v>41764</v>
+        <v>42639</v>
       </c>
       <c r="T30" t="n">
-        <v>14466</v>
+        <v>14769</v>
       </c>
       <c r="V30" t="n">
-        <v>20067</v>
+        <v>20487</v>
       </c>
     </row>
     <row r="31">
@@ -2374,16 +2374,16 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>258405</v>
+        <v>257544</v>
       </c>
       <c r="R31" t="n">
-        <v>73779</v>
+        <v>73533</v>
       </c>
       <c r="U31" t="n">
-        <v>51986</v>
+        <v>51812</v>
       </c>
       <c r="V31" t="n">
-        <v>49190</v>
+        <v>49026</v>
       </c>
     </row>
     <row r="32">
